--- a/数据导出/filter_conditions.xlsx
+++ b/数据导出/filter_conditions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,6 +634,370 @@
         <v>46129.37647059297</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{#IFNAME}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{$NET.IF.IFNAME.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{#IFNAME}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{$NET.IF.IFNAME.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{#IFALIAS}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{$NET.IF.IFALIAS.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111</v>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{#IFALIAS}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{$NET.IF.IFALIAS.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{#IFOPERSTATUS}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{$NET.IF.IFOPERSTATUS.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{#IFOPERSTATUS}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{$NET.IF.IFOPERSTATUS.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114</v>
+      </c>
+      <c r="B15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{$VFS.DEV.DEVNAME.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115</v>
+      </c>
+      <c r="B16" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{$VFS.DEV.DEVNAME.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>116</v>
+      </c>
+      <c r="B17" t="n">
+        <v>17</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{#FSTYPE}</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{$VFS.FS.FSTYPE.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>117</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{#FSTYPE}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{$VFS.FS.FSTYPE.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{#FSNAME}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{$VFS.FS.FSNAME.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119</v>
+      </c>
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{#FSNAME}</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{$VFS.FS.FSNAME.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120</v>
+      </c>
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{#FSNAME}</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{$VFS.FS.FSDEVICE.MATCHES}</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121</v>
+      </c>
+      <c r="B22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{#FSDEVICE}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{$VFS.FS.FSDEVICE.NOT_MATCHES}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NOT_MATCHES_REGEX</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
